--- a/3-需求跟踪矩阵建立/5-需求跟踪矩阵.xlsx
+++ b/3-需求跟踪矩阵建立/5-需求跟踪矩阵.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,10 @@
     <font>
       <name val="宋体"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -99,6 +103,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,9 +547,9 @@
           <t>TC-R001-01 ~ TC-R001-10</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -577,9 +584,9 @@
           <t>TC-R002-01 ~ TC-R002-06</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -614,9 +621,9 @@
           <t>TC-R003-01 ~ TC-R003-06</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -651,9 +658,9 @@
           <t>TC-R004-01 ~ TC-R004-03</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -688,9 +695,9 @@
           <t>TC-R005-01 ~ TC-R005-03</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -725,9 +732,9 @@
           <t>TC-R006-01 ~ TC-R006-06</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -762,9 +769,9 @@
           <t>TC-R007-01 ~ TC-R007-02</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -799,9 +806,9 @@
           <t>TC-NFR01-01</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -836,9 +843,9 @@
           <t>TC-NFR02-01、TC-R001-10</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -873,9 +880,9 @@
           <t>TC-NFR03-01、TC-R001-10、TC-R002-06</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>用例已就绪，待执行</t>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>自动化通过（JUnit 37/37），接口层待执行</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -895,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1005,6 +1012,18 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 已在 Windows 11 + JDK 21.0.10 + Maven 3.9.11 环境执行 mvn -B test：Tests run: 37, Failures: 0, Errors: 0，BUILD SUCCESS。覆盖借还业务、逾期状态、事务回滚、CSRF 与权限、R003 默认关闭；管理类接口与真实库并发仍待接口层执行。证据见 docs/evidence/junit-local-jdk21-20261023/。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/3-需求跟踪矩阵建立/5-需求跟踪矩阵.xlsx
+++ b/3-需求跟踪矩阵建立/5-需求跟踪矩阵.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 37/37），接口层待执行</t>
+          <t>自动化通过（JUnit 51/51）</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -916,6 +916,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1020,7 +1021,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>2026-10-23 已在 Windows 11 + JDK 21.0.10 + Maven 3.9.11 环境执行 mvn -B test：Tests run: 37, Failures: 0, Errors: 0，BUILD SUCCESS。覆盖借还业务、逾期状态、事务回滚、CSRF 与权限、R003 默认关闭；管理类接口与真实库并发仍待接口层执行。证据见 docs/evidence/junit-local-jdk21-20261023/。</t>
+          <t>2026-10-23 已在 Windows 11 + JDK 21.0.10 + Maven 3.9.11 环境执行 mvn -B test：Tests run: 51, Failures: 0, Errors: 0，BUILD SUCCESS。其中 14 个测试方法由 QA 补充（QaSupplementApiTest 12 个、QaRenewalSupplementTest 2 个），把管理类接口、检索边界、CSV 导出安全、越权借阅、续借补充分支与失败操作日志纳入自动化回归。42 条用例中 40 条已自动化覆盖，仅响应时间与真库并发两项待在有 MySQL 的环境执行。证据见 docs/evidence/junit-local-jdk21-20261023/。</t>
         </is>
       </c>
     </row>

--- a/3-需求跟踪矩阵建立/5-需求跟踪矩阵.xlsx
+++ b/3-需求跟踪矩阵建立/5-需求跟踪矩阵.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>自动化通过（JUnit 51/51）</t>
+          <t>已通过（自动化 51 项 + 接口层 20 项）</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -916,7 +916,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1022,6 +1021,18 @@
       <c r="B11" s="9" t="inlineStr">
         <is>
           <t>2026-10-23 已在 Windows 11 + JDK 21.0.10 + Maven 3.9.11 环境执行 mvn -B test：Tests run: 51, Failures: 0, Errors: 0，BUILD SUCCESS。其中 14 个测试方法由 QA 补充（QaSupplementApiTest 12 个、QaRenewalSupplementTest 2 个），把管理类接口、检索边界、CSV 导出安全、越权借阅、续借补充分支与失败操作日志纳入自动化回归。42 条用例中 40 条已自动化覆盖，仅响应时间与真库并发两项待在有 MySQL 的环境执行。证据见 docs/evidence/junit-local-jdk21-20261023/。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>2026-10-23 完成两层验证：①自动化 mvn -B test，Tests run: 51, Failures: 0, Errors: 0（JDK 21 + H2）；②接口层实测 17 项场景全部通过（本机 MySQL 8.4.4 独立实例 3308 + 应用 8081）。另完成真库并发（10 线程争抢同一副本 success=1）、借还响应时间（20 次样本 P95=22ms）、数据库一致性（四类不一致 0 行）。至此 42 条用例全部取得执行证据。证据：docs/evidence/junit-local-jdk21-20261023/ 与 docs/evidence/api-local-mysql84-20261023/。</t>
         </is>
       </c>
     </row>
